--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125723950</v>
       </c>
       <c r="B3" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125723946</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125723950</v>
       </c>
       <c r="B3" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125723946</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125723951</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125723950</v>
       </c>
       <c r="B3" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125723946</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125723951</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125723950</v>
       </c>
       <c r="B3" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125723946</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -969,6 +969,2757 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128582687</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97448</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>788348</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7370120</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128582677</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>788379</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7370277</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128582712</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>788375</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7370286</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128582690</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97454</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>788346</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7370114</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128582688</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97454</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>788159</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7370171</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128582724</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96696</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>788302</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7370354</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128582709</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>788451</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7370034</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128582706</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>788405</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7370278</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128582714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>788453</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7370034</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128582689</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97454</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>788184</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7370165</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128582707</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>788394</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7370288</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128582680</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>788379</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7370277</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128582691</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97454</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>788367</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7370037</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128582679</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>788175</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7370238</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128582723</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96696</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>788337</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7370358</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128582681</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>788333</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7370357</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128582704</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56867</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>788187</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7370165</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128582685</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>788231</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7370288</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128582682</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>788173</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7370243</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128582722</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>788379</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7370277</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128582702</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100726</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>788291</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7370202</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128582692</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80216</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>788250</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7370300</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128582683</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>788073</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7370213</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128582711</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>788379</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7370277</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128582701</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100726</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>788263</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7370214</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128582708</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>788366</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7370275</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128582713</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>788295</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7370198</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128582700</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100726</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>788369</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7370280</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Växtplats 3</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B12" t="n">
-        <v>91470</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R12" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>91470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R13" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B14" t="n">
-        <v>97454</v>
+        <v>91470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R14" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B15" t="n">
-        <v>91470</v>
+        <v>97454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R15" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128582679</v>
+        <v>128582723</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>96696</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788175</v>
+        <v>788337</v>
       </c>
       <c r="R18" t="n">
-        <v>7370238</v>
+        <v>7370358</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2308,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2339,32 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128582723</v>
+        <v>128582679</v>
       </c>
       <c r="B19" t="n">
-        <v>96696</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>788337</v>
+        <v>788175</v>
       </c>
       <c r="R19" t="n">
-        <v>7370358</v>
+        <v>7370238</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2410,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128582722</v>
+        <v>128582702</v>
       </c>
       <c r="B24" t="n">
-        <v>5177</v>
+        <v>100726</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788379</v>
+        <v>788291</v>
       </c>
       <c r="R24" t="n">
-        <v>7370277</v>
+        <v>7370202</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128582702</v>
+        <v>128582722</v>
       </c>
       <c r="B25" t="n">
-        <v>100726</v>
+        <v>5177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788291</v>
+        <v>788379</v>
       </c>
       <c r="R25" t="n">
-        <v>7370202</v>
+        <v>7370277</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582711</v>
+        <v>128582708</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>91470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788379</v>
+        <v>788366</v>
       </c>
       <c r="R28" t="n">
-        <v>7370277</v>
+        <v>7370275</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582701</v>
+        <v>128582711</v>
       </c>
       <c r="B29" t="n">
-        <v>100726</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788263</v>
+        <v>788379</v>
       </c>
       <c r="R29" t="n">
-        <v>7370214</v>
+        <v>7370277</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3395,11 +3395,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3426,32 +3421,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582708</v>
+        <v>128582701</v>
       </c>
       <c r="B30" t="n">
-        <v>91470</v>
+        <v>100726</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788366</v>
+        <v>788263</v>
       </c>
       <c r="R30" t="n">
-        <v>7370275</v>
+        <v>7370214</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3497,6 +3492,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B14" t="n">
-        <v>91470</v>
+        <v>97454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R14" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B15" t="n">
-        <v>97454</v>
+        <v>91470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R15" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582708</v>
+        <v>128582711</v>
       </c>
       <c r="B28" t="n">
-        <v>91470</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788366</v>
+        <v>788379</v>
       </c>
       <c r="R28" t="n">
-        <v>7370275</v>
+        <v>7370277</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582711</v>
+        <v>128582701</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>100726</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788379</v>
+        <v>788263</v>
       </c>
       <c r="R29" t="n">
-        <v>7370277</v>
+        <v>7370214</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3395,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3421,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582701</v>
+        <v>128582708</v>
       </c>
       <c r="B30" t="n">
-        <v>100726</v>
+        <v>91470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788263</v>
+        <v>788366</v>
       </c>
       <c r="R30" t="n">
-        <v>7370214</v>
+        <v>7370275</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3492,11 +3497,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582687</v>
       </c>
       <c r="B5" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582712</v>
+        <v>128582690</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>97460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788375</v>
+        <v>788346</v>
       </c>
       <c r="R7" t="n">
-        <v>7370286</v>
+        <v>7370114</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582690</v>
+        <v>128582688</v>
       </c>
       <c r="B8" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788346</v>
+        <v>788159</v>
       </c>
       <c r="R8" t="n">
-        <v>7370114</v>
+        <v>7370171</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582688</v>
+        <v>128582724</v>
       </c>
       <c r="B9" t="n">
-        <v>97454</v>
+        <v>96702</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788159</v>
+        <v>788302</v>
       </c>
       <c r="R9" t="n">
-        <v>7370171</v>
+        <v>7370354</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128582724</v>
+        <v>128582712</v>
       </c>
       <c r="B10" t="n">
-        <v>96696</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788302</v>
+        <v>788375</v>
       </c>
       <c r="R10" t="n">
-        <v>7370354</v>
+        <v>7370286</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1561,7 +1561,7 @@
         <v>128582709</v>
       </c>
       <c r="B11" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>128582714</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128582706</v>
       </c>
       <c r="B13" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>128582689</v>
       </c>
       <c r="B14" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>128582707</v>
       </c>
       <c r="B15" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>128582680</v>
       </c>
       <c r="B16" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>128582691</v>
       </c>
       <c r="B17" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128582723</v>
+        <v>128582679</v>
       </c>
       <c r="B18" t="n">
-        <v>96696</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788337</v>
+        <v>788175</v>
       </c>
       <c r="R18" t="n">
-        <v>7370358</v>
+        <v>7370238</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2308,6 +2308,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128582679</v>
+        <v>128582723</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>96702</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>788175</v>
+        <v>788337</v>
       </c>
       <c r="R19" t="n">
-        <v>7370238</v>
+        <v>7370358</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2405,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2439,7 +2439,7 @@
         <v>128582681</v>
       </c>
       <c r="B20" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>128582704</v>
       </c>
       <c r="B21" t="n">
-        <v>56867</v>
+        <v>56871</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>128582685</v>
       </c>
       <c r="B22" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>128582682</v>
       </c>
       <c r="B23" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>128582702</v>
       </c>
       <c r="B24" t="n">
-        <v>100726</v>
+        <v>100734</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>128582692</v>
       </c>
       <c r="B26" t="n">
-        <v>80216</v>
+        <v>80220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>128582683</v>
       </c>
       <c r="B27" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582711</v>
+        <v>128582701</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>100734</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788379</v>
+        <v>788263</v>
       </c>
       <c r="R28" t="n">
-        <v>7370277</v>
+        <v>7370214</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,32 +3329,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582701</v>
+        <v>128582708</v>
       </c>
       <c r="B29" t="n">
-        <v>100726</v>
+        <v>91476</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788263</v>
+        <v>788366</v>
       </c>
       <c r="R29" t="n">
-        <v>7370214</v>
+        <v>7370275</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3395,11 +3400,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3426,10 +3426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582708</v>
+        <v>128582711</v>
       </c>
       <c r="B30" t="n">
-        <v>91470</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3437,21 +3437,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788366</v>
+        <v>788379</v>
       </c>
       <c r="R30" t="n">
-        <v>7370275</v>
+        <v>7370277</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
         <v>128582713</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100726</v>
+        <v>100734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582687</v>
       </c>
       <c r="B5" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582690</v>
+        <v>128582724</v>
       </c>
       <c r="B7" t="n">
-        <v>97460</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788346</v>
+        <v>788302</v>
       </c>
       <c r="R7" t="n">
-        <v>7370114</v>
+        <v>7370354</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582688</v>
+        <v>128582690</v>
       </c>
       <c r="B8" t="n">
-        <v>97460</v>
+        <v>97466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788159</v>
+        <v>788346</v>
       </c>
       <c r="R8" t="n">
-        <v>7370171</v>
+        <v>7370114</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582724</v>
+        <v>128582688</v>
       </c>
       <c r="B9" t="n">
-        <v>96702</v>
+        <v>97466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788302</v>
+        <v>788159</v>
       </c>
       <c r="R9" t="n">
-        <v>7370354</v>
+        <v>7370171</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1561,7 +1561,7 @@
         <v>128582709</v>
       </c>
       <c r="B11" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>91482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R12" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B13" t="n">
-        <v>91476</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R13" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B14" t="n">
-        <v>97460</v>
+        <v>91482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R14" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B15" t="n">
-        <v>91476</v>
+        <v>97466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R15" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2143,7 +2143,7 @@
         <v>128582691</v>
       </c>
       <c r="B17" t="n">
-        <v>97460</v>
+        <v>97466</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128582679</v>
+        <v>128582723</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>96708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788175</v>
+        <v>788337</v>
       </c>
       <c r="R18" t="n">
-        <v>7370238</v>
+        <v>7370358</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2308,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2339,32 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128582723</v>
+        <v>128582679</v>
       </c>
       <c r="B19" t="n">
-        <v>96702</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>788337</v>
+        <v>788175</v>
       </c>
       <c r="R19" t="n">
-        <v>7370358</v>
+        <v>7370238</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2410,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128582702</v>
+        <v>128582722</v>
       </c>
       <c r="B24" t="n">
-        <v>100734</v>
+        <v>5177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1365</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788291</v>
+        <v>788379</v>
       </c>
       <c r="R24" t="n">
-        <v>7370202</v>
+        <v>7370277</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128582722</v>
+        <v>128582702</v>
       </c>
       <c r="B25" t="n">
-        <v>5177</v>
+        <v>100741</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>1365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788379</v>
+        <v>788291</v>
       </c>
       <c r="R25" t="n">
-        <v>7370277</v>
+        <v>7370202</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582701</v>
+        <v>128582708</v>
       </c>
       <c r="B28" t="n">
-        <v>100734</v>
+        <v>91482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788263</v>
+        <v>788366</v>
       </c>
       <c r="R28" t="n">
-        <v>7370214</v>
+        <v>7370275</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582708</v>
+        <v>128582711</v>
       </c>
       <c r="B29" t="n">
-        <v>91476</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788366</v>
+        <v>788379</v>
       </c>
       <c r="R29" t="n">
-        <v>7370275</v>
+        <v>7370277</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3426,32 +3421,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582711</v>
+        <v>128582701</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>100741</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788379</v>
+        <v>788263</v>
       </c>
       <c r="R30" t="n">
-        <v>7370277</v>
+        <v>7370214</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3497,6 +3492,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100734</v>
+        <v>100741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582724</v>
+        <v>128582690</v>
       </c>
       <c r="B7" t="n">
-        <v>96708</v>
+        <v>97466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788302</v>
+        <v>788346</v>
       </c>
       <c r="R7" t="n">
-        <v>7370354</v>
+        <v>7370114</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582690</v>
+        <v>128582688</v>
       </c>
       <c r="B8" t="n">
         <v>97466</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788346</v>
+        <v>788159</v>
       </c>
       <c r="R8" t="n">
-        <v>7370114</v>
+        <v>7370171</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582688</v>
+        <v>128582724</v>
       </c>
       <c r="B9" t="n">
-        <v>97466</v>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788159</v>
+        <v>788302</v>
       </c>
       <c r="R9" t="n">
-        <v>7370171</v>
+        <v>7370354</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B14" t="n">
-        <v>91482</v>
+        <v>97466</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R14" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B15" t="n">
-        <v>97466</v>
+        <v>91482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R15" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582687</v>
       </c>
       <c r="B5" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582690</v>
+        <v>128582724</v>
       </c>
       <c r="B7" t="n">
-        <v>97466</v>
+        <v>96710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788346</v>
+        <v>788302</v>
       </c>
       <c r="R7" t="n">
-        <v>7370114</v>
+        <v>7370354</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582688</v>
+        <v>128582712</v>
       </c>
       <c r="B8" t="n">
-        <v>97466</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788159</v>
+        <v>788375</v>
       </c>
       <c r="R8" t="n">
-        <v>7370171</v>
+        <v>7370286</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582724</v>
+        <v>128582690</v>
       </c>
       <c r="B9" t="n">
-        <v>96708</v>
+        <v>97468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788302</v>
+        <v>788346</v>
       </c>
       <c r="R9" t="n">
-        <v>7370354</v>
+        <v>7370114</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128582712</v>
+        <v>128582688</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>97468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788375</v>
+        <v>788159</v>
       </c>
       <c r="R10" t="n">
-        <v>7370286</v>
+        <v>7370171</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1561,7 +1561,7 @@
         <v>128582709</v>
       </c>
       <c r="B11" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>128582706</v>
       </c>
       <c r="B12" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128582714</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B14" t="n">
-        <v>97466</v>
+        <v>91484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R14" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B15" t="n">
-        <v>91482</v>
+        <v>97468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R15" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2143,7 +2143,7 @@
         <v>128582691</v>
       </c>
       <c r="B17" t="n">
-        <v>97466</v>
+        <v>97468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>128582723</v>
       </c>
       <c r="B18" t="n">
-        <v>96708</v>
+        <v>96710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>128582702</v>
       </c>
       <c r="B25" t="n">
-        <v>100741</v>
+        <v>100746</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>128582692</v>
       </c>
       <c r="B26" t="n">
-        <v>80220</v>
+        <v>80222</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582708</v>
+        <v>128582711</v>
       </c>
       <c r="B28" t="n">
-        <v>91482</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788366</v>
+        <v>788379</v>
       </c>
       <c r="R28" t="n">
-        <v>7370275</v>
+        <v>7370277</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582711</v>
+        <v>128582701</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>100746</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788379</v>
+        <v>788263</v>
       </c>
       <c r="R29" t="n">
-        <v>7370277</v>
+        <v>7370214</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3395,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3421,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582701</v>
+        <v>128582708</v>
       </c>
       <c r="B30" t="n">
-        <v>100741</v>
+        <v>91484</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788263</v>
+        <v>788366</v>
       </c>
       <c r="R30" t="n">
-        <v>7370214</v>
+        <v>7370275</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3492,11 +3497,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3526,7 +3526,7 @@
         <v>128582713</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100741</v>
+        <v>100746</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582724</v>
+        <v>128582712</v>
       </c>
       <c r="B7" t="n">
-        <v>96710</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788302</v>
+        <v>788375</v>
       </c>
       <c r="R7" t="n">
-        <v>7370354</v>
+        <v>7370286</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582712</v>
+        <v>128582724</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>96710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788375</v>
+        <v>788302</v>
       </c>
       <c r="R8" t="n">
-        <v>7370286</v>
+        <v>7370354</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B12" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R12" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>91484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R13" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128582722</v>
+        <v>128582702</v>
       </c>
       <c r="B24" t="n">
-        <v>5177</v>
+        <v>100752</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788379</v>
+        <v>788291</v>
       </c>
       <c r="R24" t="n">
-        <v>7370277</v>
+        <v>7370202</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128582702</v>
+        <v>128582722</v>
       </c>
       <c r="B25" t="n">
-        <v>100746</v>
+        <v>5177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788291</v>
+        <v>788379</v>
       </c>
       <c r="R25" t="n">
-        <v>7370202</v>
+        <v>7370277</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3033,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128582692</v>
+        <v>128582683</v>
       </c>
       <c r="B26" t="n">
-        <v>80222</v>
+        <v>57849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788250</v>
+        <v>788073</v>
       </c>
       <c r="R26" t="n">
-        <v>7370300</v>
+        <v>7370213</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128582683</v>
+        <v>128582692</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>80222</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788073</v>
+        <v>788250</v>
       </c>
       <c r="R27" t="n">
-        <v>7370213</v>
+        <v>7370300</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582711</v>
+        <v>128582701</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>100752</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788379</v>
+        <v>788263</v>
       </c>
       <c r="R28" t="n">
-        <v>7370277</v>
+        <v>7370214</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,32 +3329,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582701</v>
+        <v>128582711</v>
       </c>
       <c r="B29" t="n">
-        <v>100746</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788263</v>
+        <v>788379</v>
       </c>
       <c r="R29" t="n">
-        <v>7370214</v>
+        <v>7370277</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3395,11 +3400,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100746</v>
+        <v>100752</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582712</v>
+        <v>128582724</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>96710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788375</v>
+        <v>788302</v>
       </c>
       <c r="R7" t="n">
-        <v>7370286</v>
+        <v>7370354</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582724</v>
+        <v>128582690</v>
       </c>
       <c r="B8" t="n">
-        <v>96710</v>
+        <v>97468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788302</v>
+        <v>788346</v>
       </c>
       <c r="R8" t="n">
-        <v>7370354</v>
+        <v>7370114</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582690</v>
+        <v>128582688</v>
       </c>
       <c r="B9" t="n">
         <v>97468</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788346</v>
+        <v>788159</v>
       </c>
       <c r="R9" t="n">
-        <v>7370114</v>
+        <v>7370171</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128582688</v>
+        <v>128582712</v>
       </c>
       <c r="B10" t="n">
-        <v>97468</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788159</v>
+        <v>788375</v>
       </c>
       <c r="R10" t="n">
-        <v>7370171</v>
+        <v>7370286</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128582685</v>
+        <v>128582682</v>
       </c>
       <c r="B22" t="n">
-        <v>57686</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>788231</v>
+        <v>788173</v>
       </c>
       <c r="R22" t="n">
-        <v>7370288</v>
+        <v>7370243</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2701,11 +2701,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2732,10 +2727,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128582682</v>
+        <v>128582685</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>57686</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2743,21 +2738,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788173</v>
+        <v>788231</v>
       </c>
       <c r="R23" t="n">
-        <v>7370243</v>
+        <v>7370288</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2803,6 +2798,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3033,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128582683</v>
+        <v>128582692</v>
       </c>
       <c r="B26" t="n">
-        <v>57849</v>
+        <v>80222</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788073</v>
+        <v>788250</v>
       </c>
       <c r="R26" t="n">
-        <v>7370213</v>
+        <v>7370300</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128582692</v>
+        <v>128582683</v>
       </c>
       <c r="B27" t="n">
-        <v>80222</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788250</v>
+        <v>788073</v>
       </c>
       <c r="R27" t="n">
-        <v>7370300</v>
+        <v>7370213</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582687</v>
       </c>
       <c r="B5" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128582724</v>
       </c>
       <c r="B7" t="n">
-        <v>96710</v>
+        <v>96711</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582690</v>
+        <v>128582712</v>
       </c>
       <c r="B8" t="n">
-        <v>97468</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788346</v>
+        <v>788375</v>
       </c>
       <c r="R8" t="n">
-        <v>7370114</v>
+        <v>7370286</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582688</v>
+        <v>128582690</v>
       </c>
       <c r="B9" t="n">
-        <v>97468</v>
+        <v>97469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788159</v>
+        <v>788346</v>
       </c>
       <c r="R9" t="n">
-        <v>7370171</v>
+        <v>7370114</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128582712</v>
+        <v>128582688</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>97469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788375</v>
+        <v>788159</v>
       </c>
       <c r="R10" t="n">
-        <v>7370286</v>
+        <v>7370171</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1561,7 +1561,7 @@
         <v>128582709</v>
       </c>
       <c r="B11" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>91485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R12" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B13" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R13" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B14" t="n">
-        <v>91484</v>
+        <v>97469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R14" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B15" t="n">
-        <v>97468</v>
+        <v>91485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R15" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2143,7 +2143,7 @@
         <v>128582691</v>
       </c>
       <c r="B17" t="n">
-        <v>97468</v>
+        <v>97469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>128582723</v>
       </c>
       <c r="B18" t="n">
-        <v>96710</v>
+        <v>96711</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128582682</v>
+        <v>128582685</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>57686</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>788173</v>
+        <v>788231</v>
       </c>
       <c r="R22" t="n">
-        <v>7370243</v>
+        <v>7370288</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2701,6 +2701,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2727,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128582685</v>
+        <v>128582682</v>
       </c>
       <c r="B23" t="n">
-        <v>57686</v>
+        <v>57849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,21 +2743,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2762,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788231</v>
+        <v>788173</v>
       </c>
       <c r="R23" t="n">
-        <v>7370288</v>
+        <v>7370243</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2798,11 +2803,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2832,7 +2832,7 @@
         <v>128582702</v>
       </c>
       <c r="B24" t="n">
-        <v>100752</v>
+        <v>100753</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582701</v>
+        <v>128582711</v>
       </c>
       <c r="B28" t="n">
-        <v>100752</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788263</v>
+        <v>788379</v>
       </c>
       <c r="R28" t="n">
-        <v>7370214</v>
+        <v>7370277</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582711</v>
+        <v>128582701</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>100753</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788379</v>
+        <v>788263</v>
       </c>
       <c r="R29" t="n">
-        <v>7370277</v>
+        <v>7370214</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3400,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3429,7 +3429,7 @@
         <v>128582708</v>
       </c>
       <c r="B30" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100752</v>
+        <v>100753</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582687</v>
       </c>
       <c r="B5" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128582724</v>
       </c>
       <c r="B7" t="n">
-        <v>96711</v>
+        <v>96738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128582712</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>128582690</v>
       </c>
       <c r="B9" t="n">
-        <v>97469</v>
+        <v>97496</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>128582688</v>
       </c>
       <c r="B10" t="n">
-        <v>97469</v>
+        <v>97496</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128582709</v>
       </c>
       <c r="B11" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B12" t="n">
-        <v>91485</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R12" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>91512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R13" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B14" t="n">
-        <v>97469</v>
+        <v>91512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R14" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B15" t="n">
-        <v>91485</v>
+        <v>97496</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R15" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2046,7 +2046,7 @@
         <v>128582680</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>128582691</v>
       </c>
       <c r="B17" t="n">
-        <v>97469</v>
+        <v>97496</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>128582723</v>
       </c>
       <c r="B18" t="n">
-        <v>96711</v>
+        <v>96738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>128582679</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>128582681</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>128582704</v>
       </c>
       <c r="B21" t="n">
-        <v>56871</v>
+        <v>56898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>128582685</v>
       </c>
       <c r="B22" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>128582682</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>128582702</v>
       </c>
       <c r="B24" t="n">
-        <v>100753</v>
+        <v>100780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>128582692</v>
       </c>
       <c r="B26" t="n">
-        <v>80222</v>
+        <v>80249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>128582683</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582711</v>
+        <v>128582701</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>100780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788379</v>
+        <v>788263</v>
       </c>
       <c r="R28" t="n">
-        <v>7370277</v>
+        <v>7370214</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,32 +3329,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582701</v>
+        <v>128582711</v>
       </c>
       <c r="B29" t="n">
-        <v>100753</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788263</v>
+        <v>788379</v>
       </c>
       <c r="R29" t="n">
-        <v>7370214</v>
+        <v>7370277</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3395,11 +3400,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3429,7 +3429,7 @@
         <v>128582708</v>
       </c>
       <c r="B30" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>128582713</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100753</v>
+        <v>100780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582724</v>
+        <v>128582712</v>
       </c>
       <c r="B7" t="n">
-        <v>96738</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788302</v>
+        <v>788375</v>
       </c>
       <c r="R7" t="n">
-        <v>7370354</v>
+        <v>7370286</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582712</v>
+        <v>128582724</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>96738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788375</v>
+        <v>788302</v>
       </c>
       <c r="R8" t="n">
-        <v>7370286</v>
+        <v>7370354</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128582723</v>
+        <v>128582679</v>
       </c>
       <c r="B18" t="n">
-        <v>96738</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788337</v>
+        <v>788175</v>
       </c>
       <c r="R18" t="n">
-        <v>7370358</v>
+        <v>7370238</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2308,6 +2308,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128582679</v>
+        <v>128582723</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>96738</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>788175</v>
+        <v>788337</v>
       </c>
       <c r="R19" t="n">
-        <v>7370238</v>
+        <v>7370358</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2405,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582687</v>
       </c>
       <c r="B5" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128582712</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128582724</v>
       </c>
       <c r="B8" t="n">
-        <v>96738</v>
+        <v>96744</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>128582690</v>
       </c>
       <c r="B9" t="n">
-        <v>97496</v>
+        <v>97502</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>128582688</v>
       </c>
       <c r="B10" t="n">
-        <v>97496</v>
+        <v>97502</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128582709</v>
       </c>
       <c r="B11" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>91517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R12" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B13" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R13" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B14" t="n">
-        <v>91512</v>
+        <v>97502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R14" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B15" t="n">
-        <v>97496</v>
+        <v>91517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R15" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128582680</v>
+        <v>128582691</v>
       </c>
       <c r="B16" t="n">
-        <v>57876</v>
+        <v>97502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788379</v>
+        <v>788367</v>
       </c>
       <c r="R16" t="n">
-        <v>7370277</v>
+        <v>7370037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128582691</v>
+        <v>128582680</v>
       </c>
       <c r="B17" t="n">
-        <v>97496</v>
+        <v>57876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788367</v>
+        <v>788379</v>
       </c>
       <c r="R17" t="n">
-        <v>7370037</v>
+        <v>7370277</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128582679</v>
+        <v>128582723</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>96744</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788175</v>
+        <v>788337</v>
       </c>
       <c r="R18" t="n">
-        <v>7370238</v>
+        <v>7370358</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2308,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2339,32 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128582723</v>
+        <v>128582679</v>
       </c>
       <c r="B19" t="n">
-        <v>96738</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>788337</v>
+        <v>788175</v>
       </c>
       <c r="R19" t="n">
-        <v>7370358</v>
+        <v>7370238</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2410,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128582702</v>
+        <v>128582722</v>
       </c>
       <c r="B24" t="n">
-        <v>100780</v>
+        <v>5177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1365</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788291</v>
+        <v>788379</v>
       </c>
       <c r="R24" t="n">
-        <v>7370202</v>
+        <v>7370277</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128582722</v>
+        <v>128582702</v>
       </c>
       <c r="B25" t="n">
-        <v>5177</v>
+        <v>100786</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>1365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788379</v>
+        <v>788291</v>
       </c>
       <c r="R25" t="n">
-        <v>7370277</v>
+        <v>7370202</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3036,7 +3036,7 @@
         <v>128582692</v>
       </c>
       <c r="B26" t="n">
-        <v>80249</v>
+        <v>80253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>128582701</v>
       </c>
       <c r="B28" t="n">
-        <v>100780</v>
+        <v>100786</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582711</v>
+        <v>128582708</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>91517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788379</v>
+        <v>788366</v>
       </c>
       <c r="R29" t="n">
-        <v>7370277</v>
+        <v>7370275</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582708</v>
+        <v>128582711</v>
       </c>
       <c r="B30" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3437,21 +3437,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788366</v>
+        <v>788379</v>
       </c>
       <c r="R30" t="n">
-        <v>7370275</v>
+        <v>7370277</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
         <v>128582713</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100780</v>
+        <v>100786</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582687</v>
       </c>
       <c r="B5" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582724</v>
+        <v>128582690</v>
       </c>
       <c r="B8" t="n">
-        <v>96744</v>
+        <v>97509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788302</v>
+        <v>788346</v>
       </c>
       <c r="R8" t="n">
-        <v>7370354</v>
+        <v>7370114</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582690</v>
+        <v>128582688</v>
       </c>
       <c r="B9" t="n">
-        <v>97502</v>
+        <v>97509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788346</v>
+        <v>788159</v>
       </c>
       <c r="R9" t="n">
-        <v>7370114</v>
+        <v>7370171</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128582688</v>
+        <v>128582724</v>
       </c>
       <c r="B10" t="n">
-        <v>97502</v>
+        <v>96751</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788159</v>
+        <v>788302</v>
       </c>
       <c r="R10" t="n">
-        <v>7370171</v>
+        <v>7370354</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1561,7 +1561,7 @@
         <v>128582709</v>
       </c>
       <c r="B11" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>128582706</v>
       </c>
       <c r="B12" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>128582689</v>
       </c>
       <c r="B14" t="n">
-        <v>97502</v>
+        <v>97509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>128582707</v>
       </c>
       <c r="B15" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128582691</v>
+        <v>128582680</v>
       </c>
       <c r="B16" t="n">
-        <v>97502</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788367</v>
+        <v>788379</v>
       </c>
       <c r="R16" t="n">
-        <v>7370037</v>
+        <v>7370277</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128582680</v>
+        <v>128582691</v>
       </c>
       <c r="B17" t="n">
-        <v>57876</v>
+        <v>97509</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788379</v>
+        <v>788367</v>
       </c>
       <c r="R17" t="n">
-        <v>7370277</v>
+        <v>7370037</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128582723</v>
+        <v>128582679</v>
       </c>
       <c r="B18" t="n">
-        <v>96744</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788337</v>
+        <v>788175</v>
       </c>
       <c r="R18" t="n">
-        <v>7370358</v>
+        <v>7370238</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2308,6 +2308,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128582679</v>
+        <v>128582723</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>96751</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>788175</v>
+        <v>788337</v>
       </c>
       <c r="R19" t="n">
-        <v>7370238</v>
+        <v>7370358</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2405,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128582722</v>
+        <v>128582702</v>
       </c>
       <c r="B24" t="n">
-        <v>5177</v>
+        <v>100793</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788379</v>
+        <v>788291</v>
       </c>
       <c r="R24" t="n">
-        <v>7370277</v>
+        <v>7370202</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128582702</v>
+        <v>128582722</v>
       </c>
       <c r="B25" t="n">
-        <v>100786</v>
+        <v>5177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788291</v>
+        <v>788379</v>
       </c>
       <c r="R25" t="n">
-        <v>7370202</v>
+        <v>7370277</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582701</v>
+        <v>128582711</v>
       </c>
       <c r="B28" t="n">
-        <v>100786</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788263</v>
+        <v>788379</v>
       </c>
       <c r="R28" t="n">
-        <v>7370214</v>
+        <v>7370277</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582708</v>
+        <v>128582701</v>
       </c>
       <c r="B29" t="n">
-        <v>91517</v>
+        <v>100793</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788366</v>
+        <v>788263</v>
       </c>
       <c r="R29" t="n">
-        <v>7370275</v>
+        <v>7370214</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3400,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3426,10 +3426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582711</v>
+        <v>128582708</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3437,21 +3437,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788379</v>
+        <v>788366</v>
       </c>
       <c r="R30" t="n">
-        <v>7370277</v>
+        <v>7370275</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100786</v>
+        <v>100793</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582690</v>
+        <v>128582724</v>
       </c>
       <c r="B8" t="n">
-        <v>97509</v>
+        <v>96751</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788346</v>
+        <v>788302</v>
       </c>
       <c r="R8" t="n">
-        <v>7370114</v>
+        <v>7370354</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582688</v>
+        <v>128582690</v>
       </c>
       <c r="B9" t="n">
         <v>97509</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788159</v>
+        <v>788346</v>
       </c>
       <c r="R9" t="n">
-        <v>7370171</v>
+        <v>7370114</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128582724</v>
+        <v>128582688</v>
       </c>
       <c r="B10" t="n">
-        <v>96751</v>
+        <v>97509</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788302</v>
+        <v>788159</v>
       </c>
       <c r="R10" t="n">
-        <v>7370354</v>
+        <v>7370171</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B14" t="n">
-        <v>97509</v>
+        <v>91522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R14" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B15" t="n">
-        <v>91522</v>
+        <v>97509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R15" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128582679</v>
+        <v>128582723</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>96751</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788175</v>
+        <v>788337</v>
       </c>
       <c r="R18" t="n">
-        <v>7370238</v>
+        <v>7370358</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2308,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2339,32 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128582723</v>
+        <v>128582679</v>
       </c>
       <c r="B19" t="n">
-        <v>96751</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>788337</v>
+        <v>788175</v>
       </c>
       <c r="R19" t="n">
-        <v>7370358</v>
+        <v>7370238</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2410,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128582685</v>
+        <v>128582682</v>
       </c>
       <c r="B22" t="n">
-        <v>57713</v>
+        <v>57876</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>788231</v>
+        <v>788173</v>
       </c>
       <c r="R22" t="n">
-        <v>7370288</v>
+        <v>7370243</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2701,11 +2701,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2732,10 +2727,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128582682</v>
+        <v>128582685</v>
       </c>
       <c r="B23" t="n">
-        <v>57876</v>
+        <v>57713</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2743,21 +2738,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,10 +2762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788173</v>
+        <v>788231</v>
       </c>
       <c r="R23" t="n">
-        <v>7370243</v>
+        <v>7370288</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2803,6 +2798,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3033,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128582692</v>
+        <v>128582683</v>
       </c>
       <c r="B26" t="n">
-        <v>80253</v>
+        <v>57876</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788250</v>
+        <v>788073</v>
       </c>
       <c r="R26" t="n">
-        <v>7370300</v>
+        <v>7370213</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128582683</v>
+        <v>128582692</v>
       </c>
       <c r="B27" t="n">
-        <v>57876</v>
+        <v>80253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788073</v>
+        <v>788250</v>
       </c>
       <c r="R27" t="n">
-        <v>7370213</v>
+        <v>7370300</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582711</v>
+        <v>128582708</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788379</v>
+        <v>788366</v>
       </c>
       <c r="R28" t="n">
-        <v>7370277</v>
+        <v>7370275</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582701</v>
+        <v>128582711</v>
       </c>
       <c r="B29" t="n">
-        <v>100793</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788263</v>
+        <v>788379</v>
       </c>
       <c r="R29" t="n">
-        <v>7370214</v>
+        <v>7370277</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3395,11 +3395,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3426,32 +3421,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582708</v>
+        <v>128582701</v>
       </c>
       <c r="B30" t="n">
-        <v>91522</v>
+        <v>100793</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788366</v>
+        <v>788263</v>
       </c>
       <c r="R30" t="n">
-        <v>7370275</v>
+        <v>7370214</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3497,6 +3492,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -3033,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128582683</v>
+        <v>128582692</v>
       </c>
       <c r="B26" t="n">
-        <v>57876</v>
+        <v>80253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788073</v>
+        <v>788250</v>
       </c>
       <c r="R26" t="n">
-        <v>7370213</v>
+        <v>7370300</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128582692</v>
+        <v>128582683</v>
       </c>
       <c r="B27" t="n">
-        <v>80253</v>
+        <v>57876</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788250</v>
+        <v>788073</v>
       </c>
       <c r="R27" t="n">
-        <v>7370300</v>
+        <v>7370213</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582708</v>
+        <v>128582701</v>
       </c>
       <c r="B28" t="n">
-        <v>91522</v>
+        <v>100793</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788366</v>
+        <v>788263</v>
       </c>
       <c r="R28" t="n">
-        <v>7370275</v>
+        <v>7370214</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582711</v>
+        <v>128582708</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788379</v>
+        <v>788366</v>
       </c>
       <c r="R29" t="n">
-        <v>7370277</v>
+        <v>7370275</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3421,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582701</v>
+        <v>128582711</v>
       </c>
       <c r="B30" t="n">
-        <v>100793</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788263</v>
+        <v>788379</v>
       </c>
       <c r="R30" t="n">
-        <v>7370214</v>
+        <v>7370277</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3492,11 +3497,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582687</v>
       </c>
       <c r="B5" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582712</v>
+        <v>128582724</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>96755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788375</v>
+        <v>788302</v>
       </c>
       <c r="R7" t="n">
-        <v>7370286</v>
+        <v>7370354</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582724</v>
+        <v>128582712</v>
       </c>
       <c r="B8" t="n">
-        <v>96751</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788302</v>
+        <v>788375</v>
       </c>
       <c r="R8" t="n">
-        <v>7370354</v>
+        <v>7370286</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1367,7 +1367,7 @@
         <v>128582690</v>
       </c>
       <c r="B9" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>128582688</v>
       </c>
       <c r="B10" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128582709</v>
       </c>
       <c r="B11" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B12" t="n">
-        <v>91522</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R12" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R13" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1852,7 +1852,7 @@
         <v>128582707</v>
       </c>
       <c r="B14" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>128582689</v>
       </c>
       <c r="B15" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128582680</v>
+        <v>128582691</v>
       </c>
       <c r="B16" t="n">
-        <v>57876</v>
+        <v>97513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788379</v>
+        <v>788367</v>
       </c>
       <c r="R16" t="n">
-        <v>7370277</v>
+        <v>7370037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128582691</v>
+        <v>128582680</v>
       </c>
       <c r="B17" t="n">
-        <v>97509</v>
+        <v>57880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788367</v>
+        <v>788379</v>
       </c>
       <c r="R17" t="n">
-        <v>7370037</v>
+        <v>7370277</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2240,7 +2240,7 @@
         <v>128582723</v>
       </c>
       <c r="B18" t="n">
-        <v>96751</v>
+        <v>96755</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>128582679</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>128582681</v>
       </c>
       <c r="B20" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>128582704</v>
       </c>
       <c r="B21" t="n">
-        <v>56898</v>
+        <v>56901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128582682</v>
+        <v>128582685</v>
       </c>
       <c r="B22" t="n">
-        <v>57876</v>
+        <v>57717</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>788173</v>
+        <v>788231</v>
       </c>
       <c r="R22" t="n">
-        <v>7370243</v>
+        <v>7370288</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2701,6 +2701,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2727,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128582685</v>
+        <v>128582682</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>57880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,21 +2743,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2762,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788231</v>
+        <v>788173</v>
       </c>
       <c r="R23" t="n">
-        <v>7370288</v>
+        <v>7370243</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2798,11 +2803,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128582702</v>
+        <v>128582722</v>
       </c>
       <c r="B24" t="n">
-        <v>100793</v>
+        <v>5177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1365</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788291</v>
+        <v>788379</v>
       </c>
       <c r="R24" t="n">
-        <v>7370202</v>
+        <v>7370277</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128582722</v>
+        <v>128582702</v>
       </c>
       <c r="B25" t="n">
-        <v>5177</v>
+        <v>100797</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>1365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788379</v>
+        <v>788291</v>
       </c>
       <c r="R25" t="n">
-        <v>7370277</v>
+        <v>7370202</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3036,7 +3036,7 @@
         <v>128582692</v>
       </c>
       <c r="B26" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>128582683</v>
       </c>
       <c r="B27" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>128582701</v>
       </c>
       <c r="B28" t="n">
-        <v>100793</v>
+        <v>100797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582708</v>
+        <v>128582711</v>
       </c>
       <c r="B29" t="n">
-        <v>91522</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788366</v>
+        <v>788379</v>
       </c>
       <c r="R29" t="n">
-        <v>7370275</v>
+        <v>7370277</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582711</v>
+        <v>128582708</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>91526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3437,21 +3437,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788379</v>
+        <v>788366</v>
       </c>
       <c r="R30" t="n">
-        <v>7370277</v>
+        <v>7370275</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
         <v>128582713</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100793</v>
+        <v>100797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582724</v>
+        <v>128582690</v>
       </c>
       <c r="B7" t="n">
-        <v>96755</v>
+        <v>97513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788302</v>
+        <v>788346</v>
       </c>
       <c r="R7" t="n">
-        <v>7370354</v>
+        <v>7370114</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582712</v>
+        <v>128582688</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>97513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788375</v>
+        <v>788159</v>
       </c>
       <c r="R8" t="n">
-        <v>7370286</v>
+        <v>7370171</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582690</v>
+        <v>128582724</v>
       </c>
       <c r="B9" t="n">
-        <v>97513</v>
+        <v>96755</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788346</v>
+        <v>788302</v>
       </c>
       <c r="R9" t="n">
-        <v>7370114</v>
+        <v>7370354</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128582688</v>
+        <v>128582712</v>
       </c>
       <c r="B10" t="n">
-        <v>97513</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788159</v>
+        <v>788375</v>
       </c>
       <c r="R10" t="n">
-        <v>7370171</v>
+        <v>7370286</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B14" t="n">
-        <v>91526</v>
+        <v>97513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R14" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B15" t="n">
-        <v>97513</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R15" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128582691</v>
+        <v>128582680</v>
       </c>
       <c r="B16" t="n">
-        <v>97513</v>
+        <v>57880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788367</v>
+        <v>788379</v>
       </c>
       <c r="R16" t="n">
-        <v>7370037</v>
+        <v>7370277</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128582680</v>
+        <v>128582691</v>
       </c>
       <c r="B17" t="n">
-        <v>57880</v>
+        <v>97513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788379</v>
+        <v>788367</v>
       </c>
       <c r="R17" t="n">
-        <v>7370277</v>
+        <v>7370037</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128582722</v>
+        <v>128582702</v>
       </c>
       <c r="B24" t="n">
-        <v>5177</v>
+        <v>100797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788379</v>
+        <v>788291</v>
       </c>
       <c r="R24" t="n">
-        <v>7370277</v>
+        <v>7370202</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128582702</v>
+        <v>128582722</v>
       </c>
       <c r="B25" t="n">
-        <v>100797</v>
+        <v>5177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788291</v>
+        <v>788379</v>
       </c>
       <c r="R25" t="n">
-        <v>7370202</v>
+        <v>7370277</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3033,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128582692</v>
+        <v>128582683</v>
       </c>
       <c r="B26" t="n">
-        <v>80257</v>
+        <v>57880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788250</v>
+        <v>788073</v>
       </c>
       <c r="R26" t="n">
-        <v>7370300</v>
+        <v>7370213</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128582683</v>
+        <v>128582692</v>
       </c>
       <c r="B27" t="n">
-        <v>57880</v>
+        <v>80257</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788073</v>
+        <v>788250</v>
       </c>
       <c r="R27" t="n">
-        <v>7370213</v>
+        <v>7370300</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582711</v>
+        <v>128582708</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788379</v>
+        <v>788366</v>
       </c>
       <c r="R29" t="n">
-        <v>7370277</v>
+        <v>7370275</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582708</v>
+        <v>128582711</v>
       </c>
       <c r="B30" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3437,21 +3437,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788366</v>
+        <v>788379</v>
       </c>
       <c r="R30" t="n">
-        <v>7370275</v>
+        <v>7370277</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582690</v>
+        <v>128582724</v>
       </c>
       <c r="B7" t="n">
-        <v>97513</v>
+        <v>96755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788346</v>
+        <v>788302</v>
       </c>
       <c r="R7" t="n">
-        <v>7370114</v>
+        <v>7370354</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582688</v>
+        <v>128582712</v>
       </c>
       <c r="B8" t="n">
-        <v>97513</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788159</v>
+        <v>788375</v>
       </c>
       <c r="R8" t="n">
-        <v>7370171</v>
+        <v>7370286</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582724</v>
+        <v>128582690</v>
       </c>
       <c r="B9" t="n">
-        <v>96755</v>
+        <v>97513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788302</v>
+        <v>788346</v>
       </c>
       <c r="R9" t="n">
-        <v>7370354</v>
+        <v>7370114</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128582712</v>
+        <v>128582688</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>97513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788375</v>
+        <v>788159</v>
       </c>
       <c r="R10" t="n">
-        <v>7370286</v>
+        <v>7370171</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R12" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R13" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128582723</v>
+        <v>128582679</v>
       </c>
       <c r="B18" t="n">
-        <v>96755</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788337</v>
+        <v>788175</v>
       </c>
       <c r="R18" t="n">
-        <v>7370358</v>
+        <v>7370238</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2308,6 +2308,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128582679</v>
+        <v>128582723</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>96755</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>788175</v>
+        <v>788337</v>
       </c>
       <c r="R19" t="n">
-        <v>7370238</v>
+        <v>7370358</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2405,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3033,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128582683</v>
+        <v>128582692</v>
       </c>
       <c r="B26" t="n">
-        <v>57880</v>
+        <v>80257</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788073</v>
+        <v>788250</v>
       </c>
       <c r="R26" t="n">
-        <v>7370213</v>
+        <v>7370300</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128582692</v>
+        <v>128582683</v>
       </c>
       <c r="B27" t="n">
-        <v>80257</v>
+        <v>57880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788250</v>
+        <v>788073</v>
       </c>
       <c r="R27" t="n">
-        <v>7370300</v>
+        <v>7370213</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582687</v>
       </c>
       <c r="B5" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128582724</v>
       </c>
       <c r="B7" t="n">
-        <v>96755</v>
+        <v>96762</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128582712</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>128582690</v>
       </c>
       <c r="B9" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>128582688</v>
       </c>
       <c r="B10" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128582709</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R12" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>91531</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R13" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B14" t="n">
-        <v>97513</v>
+        <v>91531</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R14" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>97520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R15" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128582680</v>
+        <v>128582691</v>
       </c>
       <c r="B16" t="n">
-        <v>57880</v>
+        <v>97520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788379</v>
+        <v>788367</v>
       </c>
       <c r="R16" t="n">
-        <v>7370277</v>
+        <v>7370037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128582691</v>
+        <v>128582680</v>
       </c>
       <c r="B17" t="n">
-        <v>97513</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788367</v>
+        <v>788379</v>
       </c>
       <c r="R17" t="n">
-        <v>7370037</v>
+        <v>7370277</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128582679</v>
+        <v>128582723</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>96762</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788175</v>
+        <v>788337</v>
       </c>
       <c r="R18" t="n">
-        <v>7370238</v>
+        <v>7370358</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2308,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2339,32 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128582723</v>
+        <v>128582679</v>
       </c>
       <c r="B19" t="n">
-        <v>96755</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>788337</v>
+        <v>788175</v>
       </c>
       <c r="R19" t="n">
-        <v>7370358</v>
+        <v>7370238</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2410,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2439,7 +2439,7 @@
         <v>128582681</v>
       </c>
       <c r="B20" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>128582704</v>
       </c>
       <c r="B21" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>128582685</v>
       </c>
       <c r="B22" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>128582682</v>
       </c>
       <c r="B23" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>128582702</v>
       </c>
       <c r="B24" t="n">
-        <v>100797</v>
+        <v>100804</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>128582692</v>
       </c>
       <c r="B26" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>128582683</v>
       </c>
       <c r="B27" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>128582701</v>
       </c>
       <c r="B28" t="n">
-        <v>100797</v>
+        <v>100804</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>128582708</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>128582711</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>128582713</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100797</v>
+        <v>100804</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582687</v>
       </c>
       <c r="B5" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582724</v>
+        <v>128582690</v>
       </c>
       <c r="B7" t="n">
-        <v>96765</v>
+        <v>97528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788302</v>
+        <v>788346</v>
       </c>
       <c r="R7" t="n">
-        <v>7370354</v>
+        <v>7370114</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582712</v>
+        <v>128582688</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>97528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788375</v>
+        <v>788159</v>
       </c>
       <c r="R8" t="n">
-        <v>7370286</v>
+        <v>7370171</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582690</v>
+        <v>128582724</v>
       </c>
       <c r="B9" t="n">
-        <v>97523</v>
+        <v>96770</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788346</v>
+        <v>788302</v>
       </c>
       <c r="R9" t="n">
-        <v>7370114</v>
+        <v>7370354</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128582688</v>
+        <v>128582712</v>
       </c>
       <c r="B10" t="n">
-        <v>97523</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788159</v>
+        <v>788375</v>
       </c>
       <c r="R10" t="n">
-        <v>7370171</v>
+        <v>7370286</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1561,7 +1561,7 @@
         <v>128582709</v>
       </c>
       <c r="B11" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>128582714</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128582706</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B14" t="n">
-        <v>91533</v>
+        <v>97528</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R14" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B15" t="n">
-        <v>97523</v>
+        <v>91538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R15" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128582691</v>
+        <v>128582680</v>
       </c>
       <c r="B16" t="n">
-        <v>97523</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788367</v>
+        <v>788379</v>
       </c>
       <c r="R16" t="n">
-        <v>7370037</v>
+        <v>7370277</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128582680</v>
+        <v>128582691</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>97528</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788379</v>
+        <v>788367</v>
       </c>
       <c r="R17" t="n">
-        <v>7370277</v>
+        <v>7370037</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2240,7 +2240,7 @@
         <v>128582723</v>
       </c>
       <c r="B18" t="n">
-        <v>96765</v>
+        <v>96770</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128582722</v>
+        <v>128582702</v>
       </c>
       <c r="B24" t="n">
-        <v>5177</v>
+        <v>100812</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788379</v>
+        <v>788291</v>
       </c>
       <c r="R24" t="n">
-        <v>7370277</v>
+        <v>7370202</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128582702</v>
+        <v>128582722</v>
       </c>
       <c r="B25" t="n">
-        <v>100807</v>
+        <v>5177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788291</v>
+        <v>788379</v>
       </c>
       <c r="R25" t="n">
-        <v>7370202</v>
+        <v>7370277</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3036,7 +3036,7 @@
         <v>128582692</v>
       </c>
       <c r="B26" t="n">
-        <v>80162</v>
+        <v>80167</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>128582711</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582708</v>
+        <v>128582701</v>
       </c>
       <c r="B29" t="n">
-        <v>91533</v>
+        <v>100812</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788366</v>
+        <v>788263</v>
       </c>
       <c r="R29" t="n">
-        <v>7370275</v>
+        <v>7370214</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3395,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3421,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582701</v>
+        <v>128582708</v>
       </c>
       <c r="B30" t="n">
-        <v>100807</v>
+        <v>91538</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788263</v>
+        <v>788366</v>
       </c>
       <c r="R30" t="n">
-        <v>7370214</v>
+        <v>7370275</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3492,11 +3497,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3526,7 +3526,7 @@
         <v>128582713</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100807</v>
+        <v>100812</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582690</v>
+        <v>128582712</v>
       </c>
       <c r="B7" t="n">
-        <v>97528</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788346</v>
+        <v>788375</v>
       </c>
       <c r="R7" t="n">
-        <v>7370114</v>
+        <v>7370286</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582688</v>
+        <v>128582724</v>
       </c>
       <c r="B8" t="n">
-        <v>97528</v>
+        <v>96770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788159</v>
+        <v>788302</v>
       </c>
       <c r="R8" t="n">
-        <v>7370171</v>
+        <v>7370354</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582724</v>
+        <v>128582690</v>
       </c>
       <c r="B9" t="n">
-        <v>96770</v>
+        <v>97528</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788302</v>
+        <v>788346</v>
       </c>
       <c r="R9" t="n">
-        <v>7370354</v>
+        <v>7370114</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128582712</v>
+        <v>128582688</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>97528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788375</v>
+        <v>788159</v>
       </c>
       <c r="R10" t="n">
-        <v>7370286</v>
+        <v>7370171</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>91538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R12" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B13" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R13" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -3033,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128582692</v>
+        <v>128582683</v>
       </c>
       <c r="B26" t="n">
-        <v>80167</v>
+        <v>57883</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788250</v>
+        <v>788073</v>
       </c>
       <c r="R26" t="n">
-        <v>7370300</v>
+        <v>7370213</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128582683</v>
+        <v>128582692</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>80167</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788073</v>
+        <v>788250</v>
       </c>
       <c r="R27" t="n">
-        <v>7370213</v>
+        <v>7370300</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582711</v>
+        <v>128582701</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>100812</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788379</v>
+        <v>788263</v>
       </c>
       <c r="R28" t="n">
-        <v>7370277</v>
+        <v>7370214</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,32 +3329,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582701</v>
+        <v>128582708</v>
       </c>
       <c r="B29" t="n">
-        <v>100812</v>
+        <v>91538</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788263</v>
+        <v>788366</v>
       </c>
       <c r="R29" t="n">
-        <v>7370214</v>
+        <v>7370275</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3395,11 +3400,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3426,10 +3426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582708</v>
+        <v>128582711</v>
       </c>
       <c r="B30" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3437,21 +3437,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788366</v>
+        <v>788379</v>
       </c>
       <c r="R30" t="n">
-        <v>7370275</v>
+        <v>7370277</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582687</v>
       </c>
       <c r="B5" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582712</v>
+        <v>128582724</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>96778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788375</v>
+        <v>788302</v>
       </c>
       <c r="R7" t="n">
-        <v>7370286</v>
+        <v>7370354</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582724</v>
+        <v>128582712</v>
       </c>
       <c r="B8" t="n">
-        <v>96770</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788302</v>
+        <v>788375</v>
       </c>
       <c r="R8" t="n">
-        <v>7370354</v>
+        <v>7370286</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1367,7 +1367,7 @@
         <v>128582690</v>
       </c>
       <c r="B9" t="n">
-        <v>97528</v>
+        <v>97536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>128582688</v>
       </c>
       <c r="B10" t="n">
-        <v>97528</v>
+        <v>97536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128582709</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R12" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R13" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128582689</v>
+        <v>128582707</v>
       </c>
       <c r="B14" t="n">
-        <v>97528</v>
+        <v>91544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788184</v>
+        <v>788394</v>
       </c>
       <c r="R14" t="n">
-        <v>7370165</v>
+        <v>7370288</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128582707</v>
+        <v>128582689</v>
       </c>
       <c r="B15" t="n">
-        <v>91538</v>
+        <v>97536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>788394</v>
+        <v>788184</v>
       </c>
       <c r="R15" t="n">
-        <v>7370288</v>
+        <v>7370165</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128582680</v>
+        <v>128582691</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>97536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788379</v>
+        <v>788367</v>
       </c>
       <c r="R16" t="n">
-        <v>7370277</v>
+        <v>7370037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128582691</v>
+        <v>128582680</v>
       </c>
       <c r="B17" t="n">
-        <v>97528</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788367</v>
+        <v>788379</v>
       </c>
       <c r="R17" t="n">
-        <v>7370037</v>
+        <v>7370277</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128582723</v>
+        <v>128582679</v>
       </c>
       <c r="B18" t="n">
-        <v>96770</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788337</v>
+        <v>788175</v>
       </c>
       <c r="R18" t="n">
-        <v>7370358</v>
+        <v>7370238</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2308,6 +2308,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128582679</v>
+        <v>128582723</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>96778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>788175</v>
+        <v>788337</v>
       </c>
       <c r="R19" t="n">
-        <v>7370238</v>
+        <v>7370358</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2405,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128582702</v>
+        <v>128582722</v>
       </c>
       <c r="B24" t="n">
-        <v>100812</v>
+        <v>5177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1365</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788291</v>
+        <v>788379</v>
       </c>
       <c r="R24" t="n">
-        <v>7370202</v>
+        <v>7370277</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128582722</v>
+        <v>128582702</v>
       </c>
       <c r="B25" t="n">
-        <v>5177</v>
+        <v>100820</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>1365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788379</v>
+        <v>788291</v>
       </c>
       <c r="R25" t="n">
-        <v>7370277</v>
+        <v>7370202</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3033,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128582683</v>
+        <v>128582692</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>80168</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788073</v>
+        <v>788250</v>
       </c>
       <c r="R26" t="n">
-        <v>7370213</v>
+        <v>7370300</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128582692</v>
+        <v>128582683</v>
       </c>
       <c r="B27" t="n">
-        <v>80167</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788250</v>
+        <v>788073</v>
       </c>
       <c r="R27" t="n">
-        <v>7370300</v>
+        <v>7370213</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3230,7 +3230,7 @@
         <v>128582701</v>
       </c>
       <c r="B28" t="n">
-        <v>100812</v>
+        <v>100820</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582708</v>
+        <v>128582711</v>
       </c>
       <c r="B29" t="n">
-        <v>91538</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788366</v>
+        <v>788379</v>
       </c>
       <c r="R29" t="n">
-        <v>7370275</v>
+        <v>7370277</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128582711</v>
+        <v>128582708</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3437,21 +3437,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788379</v>
+        <v>788366</v>
       </c>
       <c r="R30" t="n">
-        <v>7370277</v>
+        <v>7370275</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3526,7 +3526,7 @@
         <v>128582713</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>128582700</v>
       </c>
       <c r="B32" t="n">
-        <v>100812</v>
+        <v>100820</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 8383-2025 artfynd.xlsx
+++ b/artfynd/A 8383-2025 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128582724</v>
+        <v>128582690</v>
       </c>
       <c r="B7" t="n">
-        <v>96778</v>
+        <v>97536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788302</v>
+        <v>788346</v>
       </c>
       <c r="R7" t="n">
-        <v>7370354</v>
+        <v>7370114</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582712</v>
+        <v>128582688</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>97536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788375</v>
+        <v>788159</v>
       </c>
       <c r="R8" t="n">
-        <v>7370286</v>
+        <v>7370171</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582690</v>
+        <v>128582724</v>
       </c>
       <c r="B9" t="n">
-        <v>97536</v>
+        <v>96778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788346</v>
+        <v>788302</v>
       </c>
       <c r="R9" t="n">
-        <v>7370114</v>
+        <v>7370354</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128582688</v>
+        <v>128582712</v>
       </c>
       <c r="B10" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788159</v>
+        <v>788375</v>
       </c>
       <c r="R10" t="n">
-        <v>7370171</v>
+        <v>7370286</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128582714</v>
+        <v>128582706</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>788453</v>
+        <v>788405</v>
       </c>
       <c r="R12" t="n">
-        <v>7370034</v>
+        <v>7370278</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128582706</v>
+        <v>128582714</v>
       </c>
       <c r="B13" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788405</v>
+        <v>788453</v>
       </c>
       <c r="R13" t="n">
-        <v>7370278</v>
+        <v>7370034</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128582691</v>
+        <v>128582680</v>
       </c>
       <c r="B16" t="n">
-        <v>97536</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788367</v>
+        <v>788379</v>
       </c>
       <c r="R16" t="n">
-        <v>7370037</v>
+        <v>7370277</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128582680</v>
+        <v>128582691</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>97536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788379</v>
+        <v>788367</v>
       </c>
       <c r="R17" t="n">
-        <v>7370277</v>
+        <v>7370037</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128582701</v>
+        <v>128582711</v>
       </c>
       <c r="B28" t="n">
-        <v>100820</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788263</v>
+        <v>788379</v>
       </c>
       <c r="R28" t="n">
-        <v>7370214</v>
+        <v>7370277</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128582711</v>
+        <v>128582701</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>100820</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788379</v>
+        <v>788263</v>
       </c>
       <c r="R29" t="n">
-        <v>7370277</v>
+        <v>7370214</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3400,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Växtplats 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
